--- a/docs/hr/employee-handbook.xlsx
+++ b/docs/hr/employee-handbook.xlsx
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">電商營運</t>
   </si>
   <si>
-    <t xml:space="preserve">小民</t>
+    <t xml:space="preserve">Aries</t>
   </si>
   <si>
     <r>
@@ -17305,7 +17305,7 @@
       <c r="A17" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>144</v>
       </c>
       <c r="C17" s="8"/>
@@ -17948,7 +17948,7 @@
       <c r="A8" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>144</v>
       </c>
       <c r="C8" s="6" t="s">
